--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E349"/>
+  <dimension ref="A1:E354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9851,6 +9851,141 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Product owner (ž/m/d)</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Erste &amp; Steiermärkische Bank d.d.</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>13. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/01c966b2-163c-11f1-af6d-0274ad0e82e3/product-owner-z-m-d?source=search_results&amp;searchId=6d130303-5b1d-4790-b98a-b1e7dedb57c4&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Razvojni inženjer za LED proizvode (m/ž)</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>PAMETNA ENERGIJA d.o.o. za projektiranje i građenje</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>22. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/350e4524-6e37-4904-9026-8b92b8eeb273/razvojni-inzenjer-za-led-proizvode-m-z?source=search_results&amp;searchId=6d130303-5b1d-4790-b98a-b1e7dedb57c4&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Poslovni analitičar za IT sustave u trgovinama (m/ž)</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Lidl Hrvatska d.o.o. k.d.</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Velika Gorica</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>12. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/4b4a012f-162a-11f1-af6d-0274ad0e82e3/poslovni-analiticar-za-it-sustave-u-trgovinama-m-z?source=search_results&amp;searchId=6d130303-5b1d-4790-b98a-b1e7dedb57c4&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Web shop specijalist (m/ž)</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Electus DGS d.o.o.</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>13. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/8ba29f91-1626-11f1-af6d-0274ad0e82e3/web-shop-specijalist-m-z?source=search_results&amp;searchId=6d130303-5b1d-4790-b98a-b1e7dedb57c4&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Vodeći specijalist za upravljanje poslovnim suradnjama (m/ž)</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>HRVATSKA POŠTANSKA BANKA, dioničko društvo</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>12. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/859b7d31-161d-11f1-af6d-0274ad0e82e3/vodeci-specijalist-za-upravljanje-poslovnim-suradnjama-m-z?source=search_results&amp;searchId=6d130303-5b1d-4790-b98a-b1e7dedb57c4&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E354"/>
+  <dimension ref="A1:E359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9986,6 +9986,141 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Specijalist za upravljanje informacijskom sigurnošću (m/ž)</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>KentBank d.d.</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>13. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/f65c5576-1704-11f1-af6d-0274ad0e82e3/specijalist-za-upravljanje-informacijskom-sigurnoscu-m-z?source=search_results&amp;searchId=2cb4399c-0c98-44ce-b863-cf8d8b31db5f&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>SAP FI vodeći specijalist  (m/ž)</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>PLAVI TIM d.o.o.</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Zagreb, Sisak, Rijeka, Osijek</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>13. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/9df0a20d-16eb-11f1-af6d-0274ad0e82e3/sap-fi-vodeci-specijalist-m-z?source=search_results&amp;searchId=2cb4399c-0c98-44ce-b863-cf8d8b31db5f&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Sistem inženjer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>HGSPOT Grupa d.o.o.</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>13. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/235571a5-51c9-4e2b-bbdf-5ec7c4f94584/sistem-inzenjer-m-z?source=search_results&amp;searchId=2cb4399c-0c98-44ce-b863-cf8d8b31db5f&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Stariji asistent voditelja kategorije za asortiman ICT roba (m/ž)</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>HGSPOT Grupa d.o.o.</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>13. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/9c3f15ec-ef6c-4e64-8daa-1198e8affccc/stariji-asistent-voditelja-kategorije-za-asortiman-ict-roba-m-z?source=search_results&amp;searchId=2cb4399c-0c98-44ce-b863-cf8d8b31db5f&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Senior Application Developer (Python, PHP, Node.js) (m/f)</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Alma Career Croatia d.o.o.</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Zagreb, hybrid, Remote</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>19. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/22c01c1a-0beb-11f1-a76c-027b2e603b13/senior-application-developer-python-php-node-js-m-f?source=search_results&amp;searchId=2cb4399c-0c98-44ce-b863-cf8d8b31db5f&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E359"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10121,6 +10121,249 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Power Electronics Engineer (m/f)</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Vertiv Croatia d.o.o.</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>04. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/35ae279f-1866-11f1-af6d-0274ad0e82e3/power-electronics-engineer-m-f?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Sistem inženjer za Windows / Citrix / VMware (m/ž)</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Addiko Bank d.d.</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>14. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/5ec99b90-16fc-11f1-af6d-0274ad0e82e3/sistem-inzenjer-za-windows-citrix-vmware-m-z?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Digital Brand &amp; Performance Designer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>DEKRA zapošljavanje d.o.o.</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>14. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/4e0a0143-17b6-11f1-af6d-0274ad0e82e3/digital-brand-performance-designer-m-z?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Razvojni inženjer za LED proizvode (m/ž)</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>PAMETNA ENERGIJA d.o.o. za projektiranje i građenje</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Rugvica</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>22. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/350e4524-6e37-4904-9026-8b92b8eeb273/razvojni-inzenjer-za-led-proizvode-m-z?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Junior Software Developer (student) (m/f)</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>LITTLE CODE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Zagreb, Split</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>14. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/bc944951-1711-11f1-af6d-0274ad0e82e3/junior-software-developer-student-m-f?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Software Developer (m/f)</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>LITTLE CODE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Zagreb, Split</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>14. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/bbeda096-1712-11f1-af6d-0274ad0e82e3/software-developer-m-f?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>IT Project Manager (m/f)</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>LITTLE CODE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Zagreb, Split</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>14. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/e52725ac-1713-11f1-af6d-0274ad0e82e3/it-project-manager-m-f?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Office Manager (m/f)</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>LITTLE CODE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Zagreb, Split</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>14. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/f7f6cb0a-1714-11f1-af6d-0274ad0e82e3/office-manager-m-f?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Razvojni inženjer za backend (m/ž)</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>KentBank d.d.</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>13. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/a4b88e1a-17bb-11f1-af6d-0274ad0e82e3/razvojni-inzenjer-za-backend-m-z?source=search_results&amp;searchId=2988baeb-5c44-45d7-adbd-fab62e8d93eb&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10364,6 +10364,60 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>IT Governance Specialist (m/f)</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Rimac Technology d.o.o.</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Zagreb (Buzin)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>16. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/c5f1568d-1882-11f1-af6d-0274ad0e82e3/it-governance-specialist-m-f?source=search_results&amp;searchId=d5789c79-c346-49fe-bee8-3f08109dddbf&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Information Security Specialist (m/f)</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Rimac Technology d.o.o.</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Zagreb (Buzin)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>16. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/c6245fd8-1882-11f1-af6d-0274ad0e82e3/information-security-specialist-m-f?source=search_results&amp;searchId=d5789c79-c346-49fe-bee8-3f08109dddbf&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E370"/>
+  <dimension ref="A1:E373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10418,6 +10418,87 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>QA &amp; Security Engineer (m/f)</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>AIRCASH d.o.o.</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>16. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/6cff7c8b-1969-11f1-af6d-0274ad0e82e3/qa-security-engineer-m-f?source=search_results&amp;searchId=9085c4ca-087c-4d80-82d4-c22faadc0601&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Tehničar u telekomunikacijama (m/ž)</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>europhone d.o.o.</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Zagreb i Zagrebačka županija, Karlovačka županija, Zadarska županija, Kutina i okolica, Splitska županija</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>26. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b19e405d-194c-11f1-af6d-0274ad0e82e3/tehnicar-u-telekomunikacijama-m-z?source=search_results&amp;searchId=9085c4ca-087c-4d80-82d4-c22faadc0601&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Administrator broadcast sustava (m/ž/d)</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Nova TV d.d.</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>16. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b60d6785-195f-11f1-af6d-0274ad0e82e3/administrator-broadcast-sustava-m-z-d?source=search_results&amp;searchId=9085c4ca-087c-4d80-82d4-c22faadc0601&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E373"/>
+  <dimension ref="A1:E377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10499,6 +10499,114 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Ekspert za sistemsku podršku (m/ž)</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>FINA gotovinski servisi d.o.o.</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>31. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b1ce57e5-e051-41e6-a5c4-c7261aa9eded/ekspert-za-sistemsku-podrsku-m-z?source=search_results&amp;searchId=c90d373c-7fa4-4c0a-85a1-de053cdbb3b7&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Stručnjak za razvoj i integraciju IT poslovnih sustava (m/ž)</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>BELUPO lijekovi i kozmetika, dioničko društvo</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Zagreb, Koprivnica</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>20. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/44478064-1bbf-11f1-95c1-0284924bb0bd/strucnjak-za-razvoj-i-integraciju-it-poslovnih-sustava-m-z?source=search_results&amp;searchId=c90d373c-7fa4-4c0a-85a1-de053cdbb3b7&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>PHP Developer - Laravel (m/ž)</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>FER PROJEKT d.o.o.</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Zadar, Zagreb</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>21. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/acd30c8b-d3b6-43f6-9275-7a1fd7f5b6a4/php-developer-laravel-m-z?source=search_results&amp;searchId=c90d373c-7fa4-4c0a-85a1-de053cdbb3b7&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>DevOps specijalist (m/ž)</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>KONČAR - Digital d.o.o.</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>20. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/11b06e03-1c61-11f1-95c1-0284924bb0bd/devops-specijalist-m-z?source=search_results&amp;searchId=c90d373c-7fa4-4c0a-85a1-de053cdbb3b7&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E377"/>
+  <dimension ref="A1:E382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10607,6 +10607,141 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Product Owner za razvoj Moj A1 / Moj Tomato aplikacija (f/m)</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>A1 Hrvatska d.o.o.</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>22. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/daa0f522-1d59-11f1-95c1-0284924bb0bd/product-owner-za-razvoj-moj-a1-moj-tomato-aplikacija-f-m?source=search_results&amp;searchId=74292b16-75f0-4b38-99b6-75f366acd861&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Solutions ICT Expert (f/m)</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>A1 Hrvatska d.o.o.</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>22. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/dae4aaae-1d59-11f1-95c1-0284924bb0bd/cloud-infrastructure-solutions-ict-expert-f-m?source=search_results&amp;searchId=74292b16-75f0-4b38-99b6-75f366acd861&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Voditelj projekta (m/ž)</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>TSG CROATIA d.o.o.</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>21. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/fd1ff89a-1d1b-11f1-95c1-0284924bb0bd/voditelj-projekta-m-z?source=search_results&amp;searchId=74292b16-75f0-4b38-99b6-75f366acd861&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>AI Content Creator – studentski posao (m/ž)</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Alma Career Croatia d.o.o.</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>22. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/41bc18aa-1dea-11f1-95c1-0284924bb0bd/ai-content-creator-studentski-posao-m-z?source=search_results&amp;searchId=74292b16-75f0-4b38-99b6-75f366acd861&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ICT Tehničar (m/ž)</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Hrvatski Telekom d.d.</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Zagreb (Žitnjak)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>31. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/241c8582-1d40-11f1-95c1-0284924bb0bd/ict-tehnicar-m-z?source=search_results&amp;searchId=74292b16-75f0-4b38-99b6-75f366acd861&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E382"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10742,6 +10742,195 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Data Engineer - mid (m/f)</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ATOMIC INTELLIGENCE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>23. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/e7a5230c-bb14-4c9b-8ef2-fa200f2890a1/data-engineer-mid-m-f?source=search_results&amp;searchId=d60ac646-a92e-4aba-bf34-838f5b579406&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Machine Learning Research Engineer (m/f)</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ATOMIC INTELLIGENCE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>23. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/47cbac0f-c111-46de-8095-efefb75ef422/machine-learning-research-engineer-m-f?source=search_results&amp;searchId=d60ac646-a92e-4aba-bf34-838f5b579406&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Software Engineer - Java/Spring Boot (m/ž)</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ATOMIC INTELLIGENCE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>23. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/5ad2bbea-57e2-444d-a0a2-d4b321627c9b/software-engineer-java-spring-boot-m-z?source=search_results&amp;searchId=d60ac646-a92e-4aba-bf34-838f5b579406&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Software Engineer – Python (AI) (m/f)</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>ATOMIC INTELLIGENCE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>23. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/56f461b2-c79b-4b94-85b8-b1d14480a05a/software-engineer-python-ai-m-f?source=search_results&amp;searchId=d60ac646-a92e-4aba-bf34-838f5b579406&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Data Engineer - Junior (m/f)</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ATOMIC INTELLIGENCE d.o.o.</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>23. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/44b89a80-574e-40be-8c96-e9442a5d3e4c/data-engineer-junior-m-f?source=search_results&amp;searchId=d60ac646-a92e-4aba-bf34-838f5b579406&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Tehnički voditelj projekata – solarne elektrane (m/ž)</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>OBNOVI SVOJ DOM d.o.o.</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>22. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/6933fa64-a299-4eeb-89dc-ef0317fcf6e6/tehnicki-voditelj-projekata-solarne-elektrane-m-z?source=search_results&amp;searchId=d60ac646-a92e-4aba-bf34-838f5b579406&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Software Engineer (m/f)</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Profesio d.o.o.</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>23. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b68d7fcc-49db-4aeb-8002-f4b53f838536/software-engineer-m-f?source=search_results&amp;searchId=d60ac646-a92e-4aba-bf34-838f5b579406&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E389"/>
+  <dimension ref="A1:E392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10931,6 +10931,87 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Support Manager (m/ž)</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>KING ICT d.o.o.</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>02. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/8fbe420e-1eda-11f1-95c1-0284924bb0bd/support-manager-m-z?source=search_results&amp;searchId=8a766505-55c5-4698-97ad-1f3382e208c9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ITSM Solutions Implementation Specialist (m/ž)</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>KING ICT d.o.o.</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>02. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/903957d0-1eda-11f1-95c1-0284924bb0bd/itsm-solutions-implementation-specialist-m-z?source=search_results&amp;searchId=8a766505-55c5-4698-97ad-1f3382e208c9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>IT Solutions Implementation Engineer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>KING ICT d.o.o.</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>02. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/90a42c28-1eda-11f1-95c1-0284924bb0bd/it-solutions-implementation-engineer-m-z?source=search_results&amp;searchId=8a766505-55c5-4698-97ad-1f3382e208c9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E392"/>
+  <dimension ref="A1:E393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11012,6 +11012,33 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Telefonski prodajni savjetnik u A1 (m/ž)</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Electus DGS d.o.o.</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Zagreb, Osijek</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>24. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/4b192aaa-1e23-11f1-95c1-0284924bb0bd/telefonski-prodajni-savjetnik-u-a1-m-z?source=search_results&amp;searchId=820010f7-8742-4d8b-b7e0-18643e0ec247&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11039,6 +11039,87 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Razvojni inženjer hardwarea (m/ž)</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Elektrokem d.o.o.</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>26. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/37d788e7-1ebe-11f1-95c1-0284924bb0bd/razvojni-inzenjer-hardwarea-m-z?source=search_results&amp;searchId=322f6981-2812-4106-89e2-30efbd390bfa&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>IT tehničar (m/ž)</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>NARODNE NOVINE d.d.</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>26. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/adc0483d-1ec5-11f1-95c1-0284924bb0bd/it-tehnicar-m-z?source=search_results&amp;searchId=322f6981-2812-4106-89e2-30efbd390bfa&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Sistem inženjer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>NARODNE NOVINE d.d.</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>26. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/a707a62d-1ec5-11f1-95c1-0284924bb0bd/sistem-inzenjer-m-z?source=search_results&amp;searchId=322f6981-2812-4106-89e2-30efbd390bfa&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E396"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11120,6 +11120,87 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Software developer - Razvoj sustava za upravljanje rizicima (IT) (ž/m/d)</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Erste &amp; Steiermärkische Bank d.d.</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>27. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/705a5726-214b-11f1-a05c-06e97b4fdde7/software-developer-razvoj-sustava-za-upravljanje-rizicima-it-z-m-d?source=search_results&amp;searchId=de6e1c74-624c-4777-a051-f4517e3796d1&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Software developer - Razvoj platnih sustava (ž/m/d)</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Erste &amp; Steiermärkische Bank d.d.</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Zagreb, Bjelovar</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>27. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/31c17d9d-214e-11f1-a05c-06e97b4fdde7/software-developer-razvoj-platnih-sustava-z-m-d?source=search_results&amp;searchId=de6e1c74-624c-4777-a051-f4517e3796d1&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>AI Engineer (ž/m/d)</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Erste &amp; Steiermärkische Bank d.d.</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>27. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/fc90b26e-2168-11f1-a05c-06e97b4fdde7/ai-engineer-z-m-d?source=search_results&amp;searchId=de6e1c74-624c-4777-a051-f4517e3796d1&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11201,6 +11201,33 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Oracle Developer (PL/SQL / APEX) (m/ž)</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Groupama osiguranje d.d.</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>06. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/9ebf2e15-21ef-11f1-a05c-06e97b4fdde7/oracle-developer-pl-sql-apex-m-z?source=search_results&amp;searchId=13585e0d-3204-429d-8123-db69144f903a&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11228,6 +11228,141 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Viši specijalist ICT tehnologije II (m/ž)</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Plinacro d.o.o.</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>28. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/a3f909d2-15a8-4246-805c-d238774321f2/visi-specijalist-ict-tehnologije-ii-m-z?source=search_results&amp;searchId=6249cd08-554f-45fa-93e4-2736d40f1973&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Samostalni specijalist / specijalistica za razvoj proizvoda</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>FINA - Financijska agencija</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>25. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/3d77640b-22b8-11f1-b5d6-06e97b4fdde7/samostalni-specijalist-specijalistica-za-razvoj-proizvoda?source=search_results&amp;searchId=6249cd08-554f-45fa-93e4-2736d40f1973&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Frontend / Mobile Developer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>CALLIDUS GRUPA d.o.o. za poslovno savjetovanje</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>29. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/76958bdc-b486-4b7a-868e-8b6eb0f65989/frontend-mobile-developer-m-z?source=search_results&amp;searchId=6249cd08-554f-45fa-93e4-2736d40f1973&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Backend Developer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>CALLIDUS GRUPA d.o.o. za poslovno savjetovanje</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>29. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/5c19e7b5-22dc-11f1-b5d6-06e97b4fdde7/backend-developer-m-z?source=search_results&amp;searchId=6249cd08-554f-45fa-93e4-2736d40f1973&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>SWIFT administrator (m/ž)</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>F.L.-SISTEM društvo s ograničenom odgovornošću za informatički inženjering, konzalting i trgovinu</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Zagreb, Rijeka</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>28. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/30c1f71f-22af-11f1-b5d6-06e97b4fdde7/swift-administrator-m-z?source=search_results&amp;searchId=6249cd08-554f-45fa-93e4-2736d40f1973&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E405"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11363,6 +11363,168 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Product manager (m/ž)</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Raiffeisenbank Austria d.d. RBA</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>30. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/0440a66c-2430-11f1-9e17-0280a8fb46bd/product-manager-m-z?source=search_results&amp;searchId=ff8c5f16-7298-48b4-b929-c04a7a8bd8ff&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Project Manager (m/ž)</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Telelink Business Services d.o.o.</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>29. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/491dd81a-22e3-11f1-b5d6-06e97b4fdde7/project-manager-m-z?source=search_results&amp;searchId=ff8c5f16-7298-48b4-b929-c04a7a8bd8ff&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Sistem administrator (m/ž)</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>KING ICT d.o.o.</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>08. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/88e2f801-2395-11f1-b5d6-06e97b4fdde7/sistem-administrator-m-z?source=search_results&amp;searchId=ff8c5f16-7298-48b4-b929-c04a7a8bd8ff&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>KING ICT d.o.o.</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>08. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/8e69d1b6-2395-11f1-b5d6-06e97b4fdde7/cybersecurity-engineer-m-z?source=search_results&amp;searchId=ff8c5f16-7298-48b4-b929-c04a7a8bd8ff&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Specijalist za upravljanje poslovnim procesima (m/ž)</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Addiko Bank d.d.</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>29. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/7c5c0e36-22d6-11f1-b5d6-06e97b4fdde7/specijalist-za-upravljanje-poslovnim-procesima-m-z?source=search_results&amp;searchId=ff8c5f16-7298-48b4-b929-c04a7a8bd8ff&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Asistent voditelja istraživanja (m/ž)</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>INOVAPRO društvo s ograničenom odgovornošću za projektiranje, inženjering i konzalting</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Split ili Zagreb</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>30. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/1345d285-4574-4feb-973c-6fe87acc263e/asistent-voditelja-istrazivanja-m-z?source=search_results&amp;searchId=ff8c5f16-7298-48b4-b929-c04a7a8bd8ff&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E411"/>
+  <dimension ref="A1:E413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11525,6 +11525,60 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>ERP Developer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>DEKRA zapošljavanje d.o.o.</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>30. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/12795bf4-2461-11f1-9e17-0280a8fb46bd/erp-developer-m-z?source=search_results&amp;searchId=27685893-2a26-4a71-b04b-e0d00b5405a0&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>ERP konzultant (m/ž)</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>DEKRA zapošljavanje d.o.o.</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>30. 03. 2026.</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/198c21e0-2461-11f1-9e17-0280a8fb46bd/erp-konzultant-m-z?source=search_results&amp;searchId=27685893-2a26-4a71-b04b-e0d00b5405a0&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E413"/>
+  <dimension ref="A1:E415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11579,6 +11579,60 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Engineer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Altpro d.o.o.</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>02. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/d8d73b7c-26a9-11f1-9e17-0280a8fb46bd/senior-embedded-software-engineer-m-z?source=search_results&amp;searchId=7d6e5c05-d878-4745-9f75-79d0649cdd84&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Key User SAP CO (m/f)</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Perutnina Ptuj - PIPO d.o.o.</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>02. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/677c045d-28b8-4e17-8fe0-2a259fc9e73a/key-user-sap-co-m-f?source=search_results&amp;searchId=7d6e5c05-d878-4745-9f75-79d0649cdd84&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E415"/>
+  <dimension ref="A1:E426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11633,6 +11633,303 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Project Manager (m/ž)</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>KING ICT d.o.o.</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>14. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/9bbeb591-2828-11f1-9e17-0280a8fb46bd/project-manager-m-z?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Senior Java Programer - Umjetnik Koda (m/ž)</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Infoart d.o.o.</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>04. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/6c2041ca-3467-402f-a434-82dbb19c0e2e/senior-java-programer-umjetnik-koda-m-z?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Stariji UI/UX dizajner (ž/m)</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Infoart d.o.o.</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>04. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/e8e19a1d-9549-4745-91c9-3070524bc29e/stariji-ui-ux-dizajner-z-m?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Business developer - George za privatne klijente (ž/m/d)</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Erste &amp; Steiermärkische Bank d.d.</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>03. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/fe65416f-278e-11f1-9e17-0280a8fb46bd/business-developer-george-za-privatne-klijente-z-m-d?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>(Senior) Java Developer (m/f)</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>K2-18b d.o.o.</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Zagreb (Buzin)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>03. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b4407f81-2768-11f1-9e17-0280a8fb46bd/senior-java-developer-m-f?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>(Senior) .NET Developer (m/f)</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>K2-18b d.o.o.</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>03. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b404a29f-2768-11f1-9e17-0280a8fb46bd/senior-net-developer-m-f?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Business Analyst (m/ž)</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>K2-18b d.o.o.</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Zagreb (Buzin)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>03. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b3bdef77-2768-11f1-9e17-0280a8fb46bd/business-analyst-m-z?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>SAP BI Stručnjak (m/ž)</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>PLAVI TIM d.o.o.</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Zagreb, Sisak, Rijeka, Osijek</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>04. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/36435bf4-8e91-4f21-854a-dd9e5a890b78/sap-bi-strucnjak-m-z?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Agent korisničke podrške u A1 (m/ž)</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Electus DGS d.o.o.</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Zagreb, Osijek</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>04. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/1429fb73-2779-11f1-9e17-0280a8fb46bd/agent-korisnicke-podrske-u-a1-m-z?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Tester (m/ž)</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Electus DGS d.o.o.</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>04. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/93d4fecb-2775-11f1-9e17-0280a8fb46bd/tester-m-z?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Customer Support Representative (ž/m/d)</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>KEKS Pay društvo s ograničenom odgovornošću za usluge</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>03. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/b243a410-278c-11f1-9e17-0280a8fb46bd/customer-support-representative-z-m-d?source=search_results&amp;searchId=27c42805-524f-4dfb-bb31-db870ad940f9&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E426"/>
+  <dimension ref="A1:E431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,141 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Mid / Senior DWH/BI Consultant (m/f)</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Koios savjetovanje d.o.o.</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>05. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/a5c02125-2824-11f1-9e17-0280a8fb46bd/mid-senior-dwh-bi-consultant-m-f?source=search_results&amp;searchId=edaac6ef-a2db-48a6-bdb5-219038f57768&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Junior DWH/BI Consultant (m/f)</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Koios savjetovanje d.o.o.</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>05. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/e2356b90-284f-11f1-9e17-0280a8fb46bd/junior-dwh-bi-consultant-m-f?source=search_results&amp;searchId=edaac6ef-a2db-48a6-bdb5-219038f57768&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>IT tehničar za korisničku podršku (m/ž)</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>VICTOR ENERGY društvo s ograničenom odgovornošću za savjetovanje i usluge</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>04. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/da4ff3f1-c1aa-4549-aa56-5c74de6cd852/it-tehnicar-za-korisnicku-podrsku-m-z?source=search_results&amp;searchId=edaac6ef-a2db-48a6-bdb5-219038f57768&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Tehničar za održavanje računalnih sustava (m/ž)</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>KM Kovnica d.o.o.</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Pisarovina</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>15. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/7da761ae-8760-48d9-8f60-c53ef7b1c8e4/tehnicar-za-odrzavanje-racunalnih-sustava-m-z?source=search_results&amp;searchId=edaac6ef-a2db-48a6-bdb5-219038f57768&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>SCCM Packaging Engineer (m/f/x)</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>STRABAG d.o.o.</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>24. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/e3dc49f2-26c7-11f1-9e17-0280a8fb46bd/sccm-packaging-engineer-m-f-x?source=search_results&amp;searchId=edaac6ef-a2db-48a6-bdb5-219038f57768&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E431"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12065,6 +12065,141 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Programer (m/ž)</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>HRVATSKA POŠTANSKA BANKA, dioničko društvo</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>06. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/0a6b3c82-2928-11f1-9e17-0280a8fb46bd/programer-m-z?source=search_results&amp;searchId=ff6c2b42-5ff6-4f49-9732-165c8c84e7a6&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>IKT Risk Manager / CISO (m/ž)</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>J&amp;T banka d.d.</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Varaždin, Zagreb</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>16. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/7e8b125e-28f4-11f1-9e17-0280a8fb46bd/ikt-risk-manager-ciso-m-z?source=search_results&amp;searchId=ff6c2b42-5ff6-4f49-9732-165c8c84e7a6&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Customer Data Analyst / Scientist (f/m)</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>A1 Hrvatska d.o.o.</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>05. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/5f582bec-28ee-11f1-9e17-0280a8fb46bd/customer-data-analyst-scientist-f-m?source=search_results&amp;searchId=ff6c2b42-5ff6-4f49-9732-165c8c84e7a6&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>IT revizor (f/m)</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>A1 Hrvatska d.o.o.</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>05. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/60c01c3d-28ee-11f1-9e17-0280a8fb46bd/it-revizor-f-m?source=search_results&amp;searchId=ff6c2b42-5ff6-4f49-9732-165c8c84e7a6&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Tehničar za telekomunikacije (m/ž)</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Hrvatski Telekom d.d.</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Omiš, Zadar, Split, Hvar, Brač, Dubrovnik, Zagreb, Mali Lošinj, Rijeka, Umag</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>08. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/f4014940-194a-11f1-af6d-0274ad0e82e3/tehnicar-za-telekomunikacije-m-z?source=search_results&amp;searchId=ff6c2b42-5ff6-4f49-9732-165c8c84e7a6&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E436"/>
+  <dimension ref="A1:E438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12200,6 +12200,60 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Platform Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Nexi Croatia d.o.o. za kartično poslovanje</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>06. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/c93b9417-29ad-11f1-9e17-0280a8fb46bd/platform-engineer-f-m-d?source=search_results&amp;searchId=f5d87896-fd0c-45fd-b619-8a44447e8753&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Mlađi stručni suradnik za upravljanje mrežnim uslugama (m/ž)</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Odašiljači i veze d.o.o.</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Zagreb</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>06. 04. 2026.</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://mojposao.hr/posao/2f4d36c3-29b9-11f1-9e17-0280a8fb46bd/mladji-strucni-suradnik-za-upravljanje-mreznim-uslugama-m-z?source=search_results&amp;searchId=f5d87896-fd0c-45fd-b619-8a44447e8753&amp;searchSource=legacy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
